--- a/src/app/modules/dashboard/excel_files/italian-muscle-building-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/italian-muscle-building-recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,95 +446,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>recipe_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>instructions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nutritional</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>serving_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prep_time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>oils</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>whole_food_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>flavor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>weight_and_muscle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>kid_approved</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>no_weekend_prep</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>holiday_recipes</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>serving_temperature</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ratting</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>recipe_tips</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>prep</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>prep_time_note</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>prep_list</t>
         </is>
@@ -558,77 +563,82 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>1493</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '2 tbsp olive oil', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '4 slices fresh mozzarella', '2 medium tomatoes, sliced', '½ cup fresh basil leaves', '1 tbsp balsamic glaze']</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Season chicken with olive oil, oregano, salt, and pepper. Grill for 6-7 minutes per side.
 2. Top each piece with mozzarella and tomato slices. Garnish with basil and drizzle with balsamic glaze.
 </t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>{"calories": "480", "protein": "55", "carbs": "7", "fiber": "2", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
       <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Season chicken with olive oil, oregano, salt, and pepper. Grill for 6-7 minutes per side.
 2. Top each piece with mozzarella and tomato slices. Garnish with basil and drizzle with balsamic glaze.
 </t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>['Season chicken with olive oil, oregano, salt, and pepper. Grill for 6-7 minutes per side.', 'Top each piece with mozzarella and tomato slices. Garnish with basil and drizzle with balsamic glaze.']</t>
         </is>
@@ -652,10 +662,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 cup cooked quinoa', '4 bell peppers, halved and hollowed', '1 tbsp olive oil', '1 small onion, diced', '2 cloves garlic, minced', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '½ cup tomato sauce']</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add turkey and cook until browned.
 2. Stir in quinoa, basil, salt, black pepper, and tomato sauce. Fill bell peppers with mixture and bake at 375°F for 25 minutes.
@@ -663,59 +678,59 @@
 </t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "56", "carbs": "38", "fiber": "6", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add turkey and cook until browned.
 2. Stir in quinoa, basil, salt, black pepper, and tomato sauce. Fill bell peppers with mixture and bake at 375°F for 25 minutes.
@@ -723,8 +738,8 @@
 </t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add turkey and cook until browned.', 'Stir in quinoa, basil, salt, black pepper, and tomato sauce. Fill bell peppers with mixture and bake at 375°F for 25 minutes.', 'Cooking time: 28 minutes']</t>
         </is>
@@ -743,82 +758,87 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italian Herb-Crusted Salmon with Spinach</t>
+          <t>Italian Herb-Crusted Salmon With Spinach</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '2 tbsp olive oil', '1 tbsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '4 cups fresh spinach']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, herbs, salt, and pepper.
 2. Grill for 5 minutes per side. Serve over sautéed spinach.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "6", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
       <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, herbs, salt, and pepper.
 2. Grill for 5 minutes per side. Serve over sautéed spinach.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>['Rub salmon with olive oil, herbs, salt, and pepper.', 'Grill for 5 minutes per side. Serve over sautéed spinach.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -842,77 +862,82 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, cubed', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '1 cup cherry tomatoes, halved', '½ cup black olives, sliced', '2 tbsp capers', '½ tsp red pepper flakes']</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.
 2. Stir in tomatoes, olives, capers, red pepper flakes. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>{"calories": "490", "protein": "54", "carbs": "8", "fiber": "2", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.
 2. Stir in tomatoes, olives, capers, red pepper flakes. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.', 'Stir in tomatoes, olives, capers, red pepper flakes. Simmer for 10 minutes.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -936,77 +961,82 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, cubed', '2 tbsp olive oil', '1 tbsp balsamic vinegar', '1 tsp dried rosemary', '½ tsp salt', '½ tsp black pepper', '2 cups mixed roasted vegetables (zucchini, bell peppers, eggplant)']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1. Toss chicken with olive oil, balsamic vinegar, rosemary, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted vegetables.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
       <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1. Toss chicken with olive oil, balsamic vinegar, rosemary, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted vegetables.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>['Toss chicken with olive oil, balsamic vinegar, rosemary, salt, and pepper.', 'Grill for 6-7 minutes per side. Serve with roasted vegetables.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -1030,77 +1060,82 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', '3 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '8 oz whole wheat pasta', '1 tbsp chopped parsley']</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Toss shrimp with pasta and parsley.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "52", "carbs": "50", "fiber": "8", "fat": "12"}</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
       <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Toss shrimp with pasta and parsley.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>['Cook pasta according to package instructions. Heat olive oil in a pan, cook garlic for 1 minute.', 'Add shrimp, salt, and pepper. Cook for 4 minutes. Toss shrimp with pasta and parsley.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -1124,77 +1159,82 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>['6 eggs', '1 lb. ground turkey', '1 tbsp olive oil', '1 cup fresh spinach, chopped', '½ cup shredded mozzarella cheese', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned. Stir in spinach and cook for 2 minutes.
 2. Whisk eggs with basil, salt, and pepper. Pour into pan. Sprinkle mozzarella on top and bake at 375°F for 15 minutes.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>{"calories": "490", "protein": "53", "carbs": "5", "fiber": "1", "fat": "22"}</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
       <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned. Stir in spinach and cook for 2 minutes.
 2. Whisk eggs with basil, salt, and pepper. Pour into pan. Sprinkle mozzarella on top and bake at 375°F for 15 minutes.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned. Stir in spinach and cook for 2 minutes.', 'Whisk eggs with basil, salt, and pepper. Pour into pan. Sprinkle mozzarella on top and bake at 375°F for 15 minutes.', 'Cooking time: 20 minutes']</t>
         </is>
@@ -1218,77 +1258,82 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, cubed', '1 tbsp olive oil', '1 cup cooked white beans', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '1 tsp dried oregano']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.
 2. Stir in beans, salt, pepper, and oregano. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "55", "carbs": "30", "fiber": "6", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
       <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.
 2. Stir in beans, salt, pepper, and oregano. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute. Add chicken, cook until browned.', 'Stir in beans, salt, pepper, and oregano. Cook for 5 minutes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -1312,77 +1357,82 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>['1 lb. lean beef steak', '1 tbsp olive oil', '1 tsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '1 cup roasted bell peppers']</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, herbs, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve with roasted bell peppers.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "10", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
       <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, herbs, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve with roasted bell peppers.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
         <is>
           <t>['Rub steak with olive oil, herbs, salt, and pepper.', 'Grill for 5-6 minutes per side. Serve with roasted bell peppers.', 'Cooking time: 12 minutes']</t>
         </is>
@@ -1406,77 +1456,82 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '2 tbsp olive oil', 'Juice of 1 lemon', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '1 cup cooked quinoa']</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.
 2. Grill for 6-7 minutes per side, then slice. Serve over quinoa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "40", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>10</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.
 2. Grill for 6-7 minutes per side, then slice. Serve over quinoa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.', 'Grill for 6-7 minutes per side, then slice. Serve over quinoa.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -1500,77 +1555,82 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '2 tbsp olive oil', '1 tbsp pesto sauce', '½ tsp salt', '½ tsp black pepper', '2 cups asparagus spears']</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, pesto, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with roasted asparagus.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "6", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
       <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
         <v>1</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, pesto, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with roasted asparagus.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>['Rub salmon with olive oil, pesto, salt, and pepper.', 'Grill for 5 minutes per side. Serve with roasted asparagus.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -1589,82 +1649,87 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Beef &amp; Mushroom Ragù over Polenta</t>
+          <t>Beef &amp; Mushroom Ragù Over Polenta</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>['1 lb. lean ground beef', '1 tbsp olive oil', '1 small onion, diced', '2 cloves garlic, minced', '1 cup mushrooms, sliced', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '1 cup cooked polenta']</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground beef and cook until browned.
 2. Stir in mushrooms, basil, salt, and pepper. Simmer for 10 minutes and serve over polenta.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "40", "fiber": "6", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>10</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
         <v>1</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground beef and cook until browned.
 2. Stir in mushrooms, basil, salt, and pepper. Simmer for 10 minutes and serve over polenta.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground beef and cook until browned.', 'Stir in mushrooms, basil, salt, and pepper. Simmer for 10 minutes and serve over polenta.', 'Cooking time: 20 minutes']</t>
         </is>
@@ -1683,82 +1748,87 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italian Baked Cod with Olives &amp; Capers</t>
+          <t>Italian Baked Cod With Olives &amp; Capers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '2 tbsp olive oil', '1 cup cherry tomatoes, halved', '¼ cup black olives, sliced', '2 tbsp capers', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F. Place cod fillets in a baking dish and drizzle with olive oil.
 2. Top with cherry tomatoes, olives, capers, oregano, salt, and pepper. Bake for 20 minutes.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>{"calories": "490", "protein": "54", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
       <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F. Place cod fillets in a baking dish and drizzle with olive oil.
 2. Top with cherry tomatoes, olives, capers, oregano, salt, and pepper. Bake for 20 minutes.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F. Place cod fillets in a baking dish and drizzle with olive oil.', 'Top with cherry tomatoes, olives, capers, oregano, salt, and pepper. Bake for 20 minutes.', 'Cooking time: 20 minutes']</t>
         </is>
@@ -1777,15 +1847,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicken Marsala with Whole Wheat Pasta</t>
+          <t>Chicken Marsala With Whole Wheat Pasta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, sliced', '1 tbsp olive oil', '1 cup mushrooms, sliced', '½ cup Marsala wine', '½ tsp salt', '½ tsp black pepper', '8 oz whole wheat pasta']</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Add mushrooms and Marsala wine, simmer for 10 minutes.
@@ -1793,59 +1868,59 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "50", "fiber": "8", "fat": "12"}</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>10</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
       <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Add mushrooms and Marsala wine, simmer for 10 minutes.
@@ -1853,8 +1928,8 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook chicken until browned.', 'Add mushrooms and Marsala wine, simmer for 10 minutes.', 'Serve over whole wheat pasta.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -1873,82 +1948,87 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eggplant Parmesan with Grilled Chicken</t>
+          <t>Eggplant Parmesan With Grilled Chicken</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 large eggplant, sliced', '1 tbsp olive oil', '1 cup marinara sauce', '½ cup shredded mozzarella', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1. Grill eggplant slices for 3 minutes per side. Layer with marinara sauce, mozzarella, salt, and pepper.
 2. Bake at 375°F for 15 minutes. Serve with grilled chicken.
 3. Cooking time: 21 minutes</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "20", "fiber": "6", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>10</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
       <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>1. Grill eggplant slices for 3 minutes per side. Layer with marinara sauce, mozzarella, salt, and pepper.
 2. Bake at 375°F for 15 minutes. Serve with grilled chicken.
 3. Cooking time: 21 minutes</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>['Grill eggplant slices for 3 minutes per side. Layer with marinara sauce, mozzarella, salt, and pepper.', 'Bake at 375°F for 15 minutes. Serve with grilled chicken.', 'Cooking time: 21 minutes']</t>
         </is>
@@ -1972,77 +2052,82 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', '3 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '1 cup cooked brown rice']</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Serve over brown rice.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "40", "fiber": "5", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'rice', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
         <v>1</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Serve over brown rice.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add shrimp, salt, and pepper. Cook for 4 minutes. Serve over brown rice.', 'Cooking time: 5 minutes']</t>
         </is>
@@ -2061,82 +2146,87 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Bolognese over Chickpea Pasta</t>
+          <t>Turkey Bolognese Over Chickpea Pasta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 small onion, diced', '2 cloves garlic, minced', '1 cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '8 oz chickpea pasta']</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground turkey and cook until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes. Serve over chickpea pasta.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "45", "fiber": "8", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
       <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
         <v>1</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground turkey and cook until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes. Serve over chickpea pasta.
 3. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook onion and garlic for 3 minutes. Add ground turkey and cook until browned.', 'Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes. Serve over chickpea pasta.', 'Cooking time: 20 minutes']</t>
         </is>
@@ -2160,10 +2250,15 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>['4 boneless, skinless chicken breasts', '1 tbsp olive oil', '½ cup ricotta cheese', '1 cup fresh spinach, chopped', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1. Slice chicken breasts to create a pocket.
 2. Mix ricotta, spinach, salt, and pepper. Stuff into chicken.
@@ -2171,59 +2266,59 @@
 4. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "54", "carbs": "6", "fiber": "2", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
       <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
         <v>1</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>1. Slice chicken breasts to create a pocket.
 2. Mix ricotta, spinach, salt, and pepper. Stuff into chicken.
@@ -2231,8 +2326,8 @@
 4. Cooking time: 20 minutes</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
         <is>
           <t>['Slice chicken breasts to create a pocket.', 'Mix ricotta, spinach, salt, and pepper. Stuff into chicken.', 'Bake at 375°F for 20 minutes.', 'Cooking time: 20 minutes']</t>
         </is>
@@ -2251,15 +2346,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italian Chicken Meatballs with Marinara</t>
+          <t>Italian Chicken Meatballs With Marinara</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>1511</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>['1 lb. ground chicken', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '1 cup marinara sauce']</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>1. Mix chicken, basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
@@ -2267,59 +2367,59 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>10</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
       <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="b">
         <v>1</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>1. Mix chicken, basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
@@ -2327,8 +2427,8 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>['Mix chicken, basil, salt, and pepper. Form into meatballs.', 'Heat olive oil in a pan, cook meatballs for 10 minutes.', 'Add marinara sauce and simmer for 5 minutes.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -2352,77 +2452,82 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>['4 tuna steaks', '2 tbsp olive oil', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '2 cups cherry tomatoes, halved']</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1. Rub tuna with olive oil, oregano, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with cherry tomato salad.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "10", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>10</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
         <v>1</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
         <is>
           <t>1. Rub tuna with olive oil, oregano, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with cherry tomato salad.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
         <is>
           <t>['Rub tuna with olive oil, oregano, salt, and pepper.', 'Grill for 5 minutes per side. Serve with cherry tomato salad.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -2446,10 +2551,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '2 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '1 cup cooked farro', '½ cup cherry tomatoes, halved']</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, basil, salt, and black pepper.
 2. Grill for 6-7 minutes per side, then slice.
@@ -2457,59 +2567,59 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "42", "fiber": "6", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>10</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
       <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
         <v>1</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, basil, salt, and black pepper.
 2. Grill for 6-7 minutes per side, then slice.
@@ -2517,8 +2627,8 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, basil, salt, and black pepper.', 'Grill for 6-7 minutes per side, then slice.', 'Serve over farro with cherry tomatoes.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -2537,15 +2647,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italian Sausage &amp; Peppers over Whole Wheat Pasta</t>
+          <t>Italian Sausage &amp; Peppers Over Whole Wheat Pasta</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>['1 lb. Italian chicken sausage, sliced', '1 tbsp olive oil', '1 cup bell peppers, sliced', '1 small onion, sliced', '½ tsp salt', '½ tsp black pepper', '8 oz whole wheat pasta']</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add peppers, onions, salt, and black pepper. Cook for 10 minutes.
@@ -2553,59 +2668,59 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "54", "carbs": "50", "fiber": "8", "fat": "12"}</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
         <v>1</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add peppers, onions, salt, and black pepper. Cook for 10 minutes.
@@ -2613,8 +2728,8 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook sausage until browned.', 'Add peppers, onions, salt, and black pepper. Cook for 10 minutes.', 'Serve over whole wheat pasta.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -2633,82 +2748,87 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Grilled Chicken Piccata with Quinoa</t>
+          <t>Grilled Chicken Piccata With Quinoa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, sliced', '1 tbsp olive oil', '2 tbsp capers', '½ cup chicken broth', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '1 cup cooked quinoa']</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Stir in capers, chicken broth, and lemon juice. Simmer for 5 minutes. Serve over quinoa.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "40", "fiber": "6", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
       <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
         <v>1</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Stir in capers, chicken broth, and lemon juice. Simmer for 5 minutes. Serve over quinoa.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook chicken until browned.', 'Stir in capers, chicken broth, and lemon juice. Simmer for 5 minutes. Serve over quinoa.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -2732,77 +2852,82 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>['2 cans tuna, drained', '1 tbsp olive oil', '1 cup white beans, cooked', '½ tsp salt', '½ tsp black pepper', '½ cup cherry tomatoes, halved']</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1. Toss tuna with olive oil, beans, salt, and black pepper.
 2. Serve with cherry tomatoes.
 3. Cooking time: 0 minutes</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
       <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
         <is>
           <t>1. Toss tuna with olive oil, beans, salt, and black pepper.
 2. Serve with cherry tomatoes.
 3. Cooking time: 0 minutes</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
         <is>
           <t>['Toss tuna with olive oil, beans, salt, and black pepper.', 'Serve with cherry tomatoes.', 'Cooking time: 0 minutes']</t>
         </is>
@@ -2821,82 +2946,87 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italian Chicken Cacciatore over Brown Rice</t>
+          <t>Italian Chicken Cacciatore Over Brown Rice</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>['1 lb. chicken thighs, skinless', '1 tbsp olive oil', '1 small onion, diced', '1 cup mushrooms, sliced', '½ cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '1 cup cooked brown rice']</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.
 2. Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over brown rice.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "42", "fiber": "6", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'rice']</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
       <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
         <v>1</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.
 2. Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over brown rice.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.', 'Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over brown rice.', 'Cooking time: 30 minutes']</t>
         </is>
@@ -2920,10 +3050,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 cup ricotta cheese', '1 tbsp olive oil', '1 cup tomato sauce', '1 large zucchini, sliced lengthwise', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Layer zucchini slices with ricotta, turkey, and tomato sauce in a baking dish.
@@ -2931,59 +3066,59 @@
 4. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "10", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
       <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
         <v>1</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Layer zucchini slices with ricotta, turkey, and tomato sauce in a baking dish.
@@ -2991,8 +3126,8 @@
 4. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Layer zucchini slices with ricotta, turkey, and tomato sauce in a baking dish.', 'Bake at 375°F for 25 minutes.', 'Cooking time: 30 minutes']</t>
         </is>
@@ -3011,82 +3146,87 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Garlic Butter Cod with Roasted Broccoli</t>
+          <t>Garlic Butter Cod With Roasted Broccoli</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '1 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups roasted broccoli']</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted broccoli.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "55", "carbs": "10", "fiber": "4", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>10</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
       <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted broccoli.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
         <is>
           <t>['Rub cod with olive oil, garlic, salt, and black pepper.', 'Bake at 375°F for 15 minutes. Serve with roasted broccoli.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -3110,77 +3250,82 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 cup spinach, chopped', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1. Mix turkey with spinach, basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "8", "fiber": "2", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
       <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>1. Mix turkey with spinach, basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>['Mix turkey with spinach, basil, salt, and pepper. Form into meatballs.', 'Heat olive oil in a pan, cook meatballs for 10 minutes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -3204,77 +3349,82 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>['1 lb. sirloin steak', '1 tbsp olive oil', '1 tbsp balsamic vinegar', '½ tsp salt', '½ tsp black pepper', '2 cups Brussels sprouts, halved']</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, balsamic vinegar, salt, and pepper. Grill for 5 minutes per side.
 2. Roast Brussels sprouts at 375°F for 20 minutes.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "15", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>10</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
       <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
         <v>1</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, balsamic vinegar, salt, and pepper. Grill for 5 minutes per side.
 2. Roast Brussels sprouts at 375°F for 20 minutes.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
         <is>
           <t>['Rub steak with olive oil, balsamic vinegar, salt, and pepper. Grill for 5 minutes per side.', 'Roast Brussels sprouts at 375°F for 20 minutes.', 'Cooking time: 30 minutes']</t>
         </is>
@@ -3298,77 +3448,82 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', 'Juice of 1 lemon', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '1 cup cooked brown rice']</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve over brown rice.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "42", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>10</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'rice']</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
       <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
         <v>1</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve over brown rice.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, lemon juice, oregano, salt, and pepper.', 'Grill for 6-7 minutes per side. Serve over brown rice.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -3387,82 +3542,87 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italian Herb Grilled Chicken with Roasted Sweet Potatoes</t>
+          <t>Italian Herb Grilled Chicken With Roasted Sweet Potatoes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '1 tsp dried rosemary', '½ tsp salt', '½ tsp black pepper', '2 cups roasted sweet potatoes']</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, rosemary, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "40", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>10</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
       <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
         <v>1</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, rosemary, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, rosemary, salt, and black pepper.', 'Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -3486,77 +3646,82 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>1524</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 zucchinis, spiralized']</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Toss with zucchini noodles. Serve.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>10</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'noodles']</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
       <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
         <v>1</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Toss with zucchini noodles. Serve.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add shrimp, salt, and pepper. Cook for 4 minutes. Toss with zucchini noodles. Serve.', 'Cooking time: 5 minutes']</t>
         </is>
@@ -3580,77 +3745,82 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 tbsp olive oil', '½ cup sun-dried tomatoes, chopped', '1 cup cooked quinoa', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1. Toss chicken with olive oil, sun-dried tomatoes, salt, and pepper.
 2. Serve over cooked quinoa. Serve.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "40", "fiber": "6", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>10</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
       <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
         <v>1</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>1. Toss chicken with olive oil, sun-dried tomatoes, salt, and pepper.
 2. Serve over cooked quinoa. Serve.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
         <is>
           <t>['Toss chicken with olive oil, sun-dried tomatoes, salt, and pepper.', 'Serve over cooked quinoa. Serve.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -3674,77 +3844,82 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '1 tsp dried oregano']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>1. Mix turkey, salt, pepper, and oregano. Form into a loaf.
 2. Bake at 375°F for 25 minutes. Serve with tomato sauce.
 3. Cooking time: 25 minutes</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>4</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>10</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
       <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
         <v>1</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>1. Mix turkey, salt, pepper, and oregano. Form into a loaf.
 2. Bake at 375°F for 25 minutes. Serve with tomato sauce.
 3. Cooking time: 25 minutes</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
         <is>
           <t>['Mix turkey, salt, pepper, and oregano. Form into a loaf.', 'Bake at 375°F for 25 minutes. Serve with tomato sauce.', 'Cooking time: 25 minutes']</t>
         </is>
@@ -3768,77 +3943,82 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, cubed', '1 tbsp olive oil', '1 cup cooked chickpeas', '½ tsp salt', '½ tsp black pepper', '1 tsp dried basil']</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Stir in chickpeas, salt, pepper, and basil. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
       <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
         <v>1</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook chicken until browned.
 2. Stir in chickpeas, salt, pepper, and basil. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook chicken until browned.', 'Stir in chickpeas, salt, pepper, and basil. Cook for 5 minutes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -3862,77 +4042,82 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, sliced', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups steamed broccoli']</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add chicken, salt, and pepper. Cook for 6 minutes. Serve with steamed broccoli.
 3. Cooking time: 7 minutes</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "8", "fiber": "4", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>10</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
       <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
         <v>1</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add chicken, salt, and pepper. Cook for 6 minutes. Serve with steamed broccoli.
 3. Cooking time: 7 minutes</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add chicken, salt, and pepper. Cook for 6 minutes. Serve with steamed broccoli.', 'Cooking time: 7 minutes']</t>
         </is>
@@ -3956,77 +4141,82 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>['1 lb. lean beef steak', '1 tbsp olive oil', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '2 cups roasted Brussels sprouts']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, oregano, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "15", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>10</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
       <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="b">
         <v>1</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, oregano, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
         <is>
           <t>['Rub steak with olive oil, oregano, salt, and pepper.', 'Grill for 5-6 minutes per side. Serve with roasted Brussels sprouts.', 'Cooking time: 12 minutes']</t>
         </is>
@@ -4050,77 +4240,82 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '8 oz whole wheat pasta']</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes. Toss with pasta, then serve.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "52", "carbs": "50", "fiber": "8", "fat": "12"}</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>10</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
       <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="b">
         <v>1</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes. Toss with pasta, then serve.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
         <is>
           <t>['Cook pasta according to package instructions.', 'Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes. Toss with pasta, then serve.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -4144,77 +4339,82 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '1 cup roasted bell peppers']</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in basil, salt, and pepper. Serve with roasted bell peppers.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "54", "carbs": "15", "fiber": "4", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>10</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
       <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="b">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in basil, salt, and pepper. Serve with roasted bell peppers.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in basil, salt, and pepper. Serve with roasted bell peppers.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -4238,77 +4438,82 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>1532</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 tbsp olive oil', '½ tsp salt', '½ tsp black pepper', '2 cups fresh spinach']</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side, then slice. Serve over fresh spinach.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "8", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>10</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
       <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="b">
         <v>1</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side, then slice. Serve over fresh spinach.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and pepper.', 'Grill for 6-7 minutes per side, then slice. Serve over fresh spinach.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -4332,77 +4537,82 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>1533</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>['1 lb. sirloin steak', '1 tbsp olive oil', '1 tbsp balsamic vinegar', '½ tsp salt', '½ tsp black pepper', '2 cups roasted eggplant']</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, balsamic vinegar, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "12", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>4</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>10</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
       <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="b">
         <v>1</v>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, balsamic vinegar, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
         <is>
           <t>['Rub steak with olive oil, balsamic vinegar, salt, and pepper.', 'Grill for 5 minutes per side. Serve with roasted eggplant.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -4426,77 +4636,82 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>1534</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '2 tbsp olive oil', '1 tsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '2 cups asparagus']</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, Italian herbs, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with steamed asparagus.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "7", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
       <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="b">
         <v>1</v>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
         <is>
           <t>1. Rub salmon with olive oil, Italian herbs, salt, and pepper.
 2. Grill for 5 minutes per side. Serve with steamed asparagus.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
         <is>
           <t>['Rub salmon with olive oil, Italian herbs, salt, and pepper.', 'Grill for 5 minutes per side. Serve with steamed asparagus.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -4515,82 +4730,87 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italian Chicken Meatballs with Zucchini Noodles</t>
+          <t>Italian Chicken Meatballs With Zucchini Noodles</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>['1 lb. ground chicken', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '2 zucchinis, spiralized']</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>1. Mix ground chicken with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes. Serve over zucchini noodles.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "12", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>4</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>10</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
       <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="b">
         <v>1</v>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
         <is>
           <t>1. Mix ground chicken with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes. Serve over zucchini noodles.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
         <is>
           <t>['Mix ground chicken with basil, salt, and pepper. Form into meatballs.', 'Heat olive oil in a pan, cook meatballs for 10 minutes. Serve over zucchini noodles.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -4609,82 +4829,87 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lemon Garlic Shrimp with Brown Rice</t>
+          <t>Lemon Garlic Shrimp With Brown Rice</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '1 cup cooked brown rice']</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over brown rice.
 3. Cooking time: 4 minutes</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "40", "fiber": "5", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>4</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>10</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'rice', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
       <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="b">
         <v>1</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over brown rice.
 3. Cooking time: 4 minutes</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.', 'Serve over brown rice.', 'Cooking time: 4 minutes']</t>
         </is>
@@ -4703,82 +4928,87 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italian Chicken Sausage &amp; Peppers over Quinoa</t>
+          <t>Italian Chicken Sausage &amp; Peppers Over Quinoa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>['1 lb. Italian chicken sausage, sliced', '1 tbsp olive oil', '1 cup bell peppers, sliced', '½ tsp salt', '½ tsp black pepper', '1 cup cooked quinoa']</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add peppers, salt, and pepper. Cook for 10 minutes. Serve over quinoa.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "54", "carbs": "40", "fiber": "6", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>10</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
       <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="b">
         <v>1</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add peppers, salt, and pepper. Cook for 10 minutes. Serve over quinoa.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook sausage until browned.', 'Add peppers, salt, and pepper. Cook for 10 minutes. Serve over quinoa.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -4797,82 +5027,87 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italian Grilled Chicken with Tomato &amp; Olive Salsa</t>
+          <t>Italian Grilled Chicken With Tomato &amp; Olive Salsa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '½ tsp salt', '½ tsp black pepper', '½ cup cherry tomatoes, halved', '¼ cup black olives, sliced']</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Top with tomato and olive salsa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>4</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>10</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
       <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
         <v>1</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Top with tomato and olive salsa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and pepper.', 'Grill for 6-7 minutes per side. Top with tomato and olive salsa.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -4896,77 +5131,82 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>['2 cans tuna, drained', '1 tbsp olive oil', '1 cup cannellini beans', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1. Toss tuna with olive oil, beans, salt, and black pepper.
 2. Serve as a protein-packed bowl.
 3. Cooking time: 0 minutes</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>10</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
       <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="b">
         <v>1</v>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
         <is>
           <t>1. Toss tuna with olive oil, beans, salt, and black pepper.
 2. Serve as a protein-packed bowl.
 3. Cooking time: 0 minutes</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
         <is>
           <t>['Toss tuna with olive oil, beans, salt, and black pepper.', 'Serve as a protein-packed bowl.', 'Cooking time: 0 minutes']</t>
         </is>
@@ -4985,82 +5225,87 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Garlic Butter Cod with Roasted Bell Peppers</t>
+          <t>Garlic Butter Cod With Roasted Bell Peppers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '1 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups roasted bell peppers']</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted bell peppers.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "55", "carbs": "10", "fiber": "4", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>10</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
       <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="b">
         <v>1</v>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted bell peppers.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>['Rub cod with olive oil, garlic, salt, and black pepper.', 'Bake at 375°F for 15 minutes. Serve with roasted bell peppers.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -5079,15 +5324,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italian Turkey Bolognese over Whole Wheat Pasta</t>
+          <t>Italian Turkey Bolognese Over Whole Wheat Pasta</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '8 oz whole wheat pasta']</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.
@@ -5095,59 +5345,59 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "45", "fiber": "8", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>10</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
       <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="b">
         <v>1</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.
@@ -5155,8 +5405,8 @@
 4. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.', 'Serve over whole wheat pasta.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -5175,82 +5425,87 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lemon Herb Grilled Chicken with Roasted Broccoli</t>
+          <t>Lemon Herb Grilled Chicken With Roasted Broccoli</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', 'Juice of 1 lemon', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '2 cups roasted broccoli']</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted broccoli.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>4</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>10</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
       <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="b">
         <v>1</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, lemon juice, oregano, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted broccoli.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, lemon juice, oregano, salt, and black pepper.', 'Grill for 6-7 minutes per side. Serve with roasted broccoli.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -5274,77 +5529,82 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>1543</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '8 oz chickpea pasta']</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. Heat olive oil in a pan, cook shrimp with basil, salt, and pepper for 4 minutes. Toss with pasta.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "54", "carbs": "40", "fiber": "7", "fat": "12"}</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>4</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>10</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'pasta']</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
       <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="b">
         <v>1</v>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. Heat olive oil in a pan, cook shrimp with basil, salt, and pepper for 4 minutes. Toss with pasta.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
         <is>
           <t>['Cook pasta according to package instructions.', 'Heat olive oil in a pan, cook shrimp with basil, salt, and pepper for 4 minutes. Toss with pasta.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -5368,77 +5628,82 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tsp dried rosemary', '½ tsp salt', '½ tsp black pepper', '2 cups roasted cauliflower']</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in rosemary, salt, and black pepper. Serve with roasted cauliflower.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "54", "carbs": "12", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>4</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>10</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
       <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="b">
         <v>1</v>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in rosemary, salt, and black pepper. Serve with roasted cauliflower.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in rosemary, salt, and black pepper. Serve with roasted cauliflower.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -5462,77 +5727,82 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '1 tbsp olive oil', '1 tbsp balsamic vinegar', '½ tsp salt', '½ tsp black pepper', '2 cups roasted sweet potatoes']</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "40", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>10</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
       <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="b">
         <v>1</v>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.', 'Grill for 6-7 minutes per side. Serve with roasted sweet potatoes.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -5556,77 +5826,82 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>['1 lb. Italian chicken sausage, sliced', '1 tbsp olive oil', '2 zucchinis, sliced', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add zucchini, salt, and black pepper. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "54", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>4</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>10</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'stir-fry']</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
       <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="b">
         <v>1</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook sausage until browned.
 2. Add zucchini, salt, and black pepper. Cook for 5 minutes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook sausage until browned.', 'Add zucchini, salt, and black pepper. Cook for 5 minutes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -5650,77 +5925,82 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 tbsp olive oil', '1 cup white beans, cooked', '½ tsp salt', '½ tsp black pepper', '1 tsp dried basil']</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and basil.
 2. Grill for 6-7 minutes per side. Serve with white beans.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>4</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>10</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
       <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="b">
         <v>1</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and basil.
 2. Grill for 6-7 minutes per side. Serve with white beans.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and basil.', 'Grill for 6-7 minutes per side. Serve with white beans.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -5739,82 +6019,87 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Garlic Butter Cod with Roasted Brussels Sprouts</t>
+          <t>Garlic Butter Cod With Roasted Brussels Sprouts</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '1 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups roasted Brussels sprouts']</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted Brussels sprouts.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "55", "carbs": "12", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>4</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>10</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
       <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="b">
         <v>1</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, garlic, salt, and black pepper.
 2. Bake at 375°F for 15 minutes. Serve with roasted Brussels sprouts.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
         <is>
           <t>['Rub cod with olive oil, garlic, salt, and black pepper.', 'Bake at 375°F for 15 minutes. Serve with roasted Brussels sprouts.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -5838,77 +6123,82 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '1 cup cooked quinoa']</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over quinoa.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "40", "fiber": "6", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>4</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>10</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N58" t="b">
-        <v>0</v>
-      </c>
       <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="b">
         <v>1</v>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over quinoa.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.', 'Serve over quinoa.', 'Cooking time: 5 minutes']</t>
         </is>
@@ -5932,77 +6222,82 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '½ tsp salt', '½ tsp black pepper', '½ cup cherry tomatoes, halved', '½ cup fresh basil leaves']</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Top with tomato basil salsa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "55", "carbs": "10", "fiber": "3", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>4</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>10</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N59" t="b">
-        <v>0</v>
-      </c>
       <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="b">
         <v>1</v>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Top with tomato basil salsa.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr">
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and pepper.', 'Grill for 6-7 minutes per side. Top with tomato basil salsa.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -6021,15 +6316,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italian Turkey Bolognese over Spaghetti Squash</t>
+          <t>Italian Turkey Bolognese Over Spaghetti Squash</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '2 cups cooked spaghetti squash']</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.
@@ -6037,59 +6337,59 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>4</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>10</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N60" t="b">
-        <v>0</v>
-      </c>
       <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="b">
         <v>1</v>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.
@@ -6097,8 +6397,8 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in tomato sauce, salt, and pepper. Simmer for 10 minutes.', 'Serve over spaghetti squash.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -6117,82 +6417,87 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italian Grilled Chicken with Pesto &amp; Roasted Red Peppers</t>
+          <t>Italian Grilled Chicken With Pesto &amp; Roasted Red Peppers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '1 tbsp pesto sauce', '½ tsp salt', '½ tsp black pepper', '1 cup roasted red peppers']</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and black pepper. Grill for 6-7 minutes per side.
 2. Top with pesto and serve with roasted red peppers.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>4</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>10</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
       <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="b">
         <v>1</v>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and black pepper. Grill for 6-7 minutes per side.
 2. Top with pesto and serve with roasted red peppers.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and black pepper. Grill for 6-7 minutes per side.', 'Top with pesto and serve with roasted red peppers.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -6216,77 +6521,82 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>1553</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups roasted asparagus']</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Serve with roasted asparagus.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "8", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>4</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>10</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N62" t="b">
-        <v>0</v>
-      </c>
       <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="b">
         <v>1</v>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add shrimp, salt, and pepper. Cook for 4 minutes. Serve with roasted asparagus.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr">
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add shrimp, salt, and pepper. Cook for 4 minutes. Serve with roasted asparagus.', 'Cooking time: 5 minutes']</t>
         </is>
@@ -6310,77 +6620,82 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '6 eggs', '1 tbsp olive oil', '1 cup fresh spinach, chopped', '½ tsp salt', '½ tsp black pepper']</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned. Add spinach and cook for 2 minutes.
 2. Whisk eggs, salt, and pepper, then pour into pan. Stir until eggs are fully cooked.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "6", "fiber": "2", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>4</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>10</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N63" t="b">
-        <v>0</v>
-      </c>
       <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="b">
         <v>1</v>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned. Add spinach and cook for 2 minutes.
 2. Whisk eggs, salt, and pepper, then pour into pan. Stir until eggs are fully cooked.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr">
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned. Add spinach and cook for 2 minutes.', 'Whisk eggs, salt, and pepper, then pour into pan. Stir until eggs are fully cooked.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -6404,77 +6719,82 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '2 tbsp olive oil', 'Juice of 1 lemon', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '1 cup cooked brown rice']</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, lemon juice, oregano, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve over brown rice.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "55", "carbs": "40", "fiber": "6", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>4</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>10</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N64" t="b">
-        <v>0</v>
-      </c>
       <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="b">
         <v>1</v>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
         <is>
           <t>1. Rub cod with olive oil, lemon juice, oregano, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve over brown rice.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr">
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
         <is>
           <t>['Rub cod with olive oil, lemon juice, oregano, salt, and black pepper.', 'Grill for 5 minutes per side. Serve over brown rice.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -6498,10 +6818,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>['1 lb. ground chicken', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '2 zucchinis, sliced and roasted']</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>1. Mix ground chicken with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
@@ -6509,59 +6834,59 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "12", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>4</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>10</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
       <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="b">
         <v>1</v>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
         <is>
           <t>1. Mix ground chicken with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes.
@@ -6569,8 +6894,8 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
         <is>
           <t>['Mix ground chicken with basil, salt, and pepper. Form into meatballs.', 'Heat olive oil in a pan, cook meatballs for 10 minutes.', 'Serve with roasted zucchini.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -6594,77 +6919,82 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>['1 lb. sirloin steak', '1 tbsp olive oil', '1 tsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '2 cups fresh spinach']</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, Italian herbs, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve over fresh spinach.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "10", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>4</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>10</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
       <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="b">
         <v>1</v>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
         <is>
           <t>1. Rub steak with olive oil, Italian herbs, salt, and pepper.
 2. Grill for 5-6 minutes per side. Serve over fresh spinach.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
         <is>
           <t>['Rub steak with olive oil, Italian herbs, salt, and pepper.', 'Grill for 5-6 minutes per side. Serve over fresh spinach.', 'Cooking time: 12 minutes']</t>
         </is>
@@ -6683,82 +7013,87 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italian Balsamic Chicken with Roasted Brussels Sprouts</t>
+          <t>Italian Balsamic Chicken With Roasted Brussels Sprouts</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '1 tbsp olive oil', '1 tbsp balsamic vinegar', '½ tsp salt', '½ tsp black pepper', '2 cups roasted Brussels sprouts']</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "15", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>4</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>10</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
       <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="b">
         <v>1</v>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, balsamic vinegar, salt, and black pepper.', 'Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -6782,10 +7117,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>1559</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, sliced', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups green beans, roasted']</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add chicken, salt, and pepper. Cook for 6 minutes.
@@ -6793,59 +7133,59 @@
 4. Cooking time: 7 minutes</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>{"calories": "500", "protein": "54", "carbs": "8", "fiber": "4", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>4</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>10</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
       <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="b">
         <v>1</v>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add chicken, salt, and pepper. Cook for 6 minutes.
@@ -6853,8 +7193,8 @@
 4. Cooking time: 7 minutes</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add chicken, salt, and pepper. Cook for 6 minutes.', 'Serve with roasted green beans.', 'Cooking time: 7 minutes']</t>
         </is>
@@ -6878,77 +7218,82 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>['4 swordfish fillets', '2 tbsp olive oil', '1 tsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '2 cups steamed broccoli']</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>1. Rub swordfish with olive oil, Italian herbs, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve with steamed broccoli.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "8", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>10</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
       <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="b">
         <v>1</v>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
         <is>
           <t>1. Rub swordfish with olive oil, Italian herbs, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve with steamed broccoli.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
         <is>
           <t>['Rub swordfish with olive oil, Italian herbs, salt, and black pepper.', 'Grill for 5 minutes per side. Serve with steamed broccoli.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -6967,82 +7312,87 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicken Cacciatore over Quinoa</t>
+          <t>Chicken Cacciatore Over Quinoa</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>['1 lb. chicken thighs, skinless', '1 tbsp olive oil', '1 small onion, diced', '1 cup mushrooms, sliced', '½ cup tomato sauce', '½ tsp salt', '½ tsp black pepper', '1 cup cooked quinoa']</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.
 2. Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over quinoa.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "42", "fiber": "6", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>10</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
       <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="b">
         <v>1</v>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.
 2. Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over quinoa.
 3. Cooking time: 30 minutes</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook onions and mushrooms for 3 minutes. Add chicken and cook until browned.', 'Stir in tomato sauce, salt, and black pepper. Simmer for 20 minutes. Serve over quinoa.', 'Cooking time: 30 minutes']</t>
         </is>
@@ -7066,77 +7416,82 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 cup white beans, cooked', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '½ cup cherry tomatoes, halved']</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in white beans, basil, salt, black pepper, and tomatoes. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>4</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>10</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
       <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="b">
         <v>1</v>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in white beans, basil, salt, black pepper, and tomatoes. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in white beans, basil, salt, black pepper, and tomatoes. Simmer for 10 minutes.', 'Cooking time: 15 minutes']</t>
         </is>
@@ -7155,82 +7510,87 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Grilled Italian Turkey Burgers with Roasted Peppers</t>
+          <t>Grilled Italian Turkey Burgers With Roasted Peppers</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '4 whole wheat buns', '1 cup roasted bell peppers']</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>1. Mix ground turkey with oregano, salt, and pepper. Form into patties.
 2. Grill for 5-6 minutes per side. Serve on whole wheat buns with roasted bell peppers.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "54", "carbs": "42", "fiber": "6", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>4</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>10</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
       <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="b">
         <v>1</v>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
         <is>
           <t>1. Mix ground turkey with oregano, salt, and pepper. Form into patties.
 2. Grill for 5-6 minutes per side. Serve on whole wheat buns with roasted bell peppers.
 3. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
         <is>
           <t>['Mix ground turkey with oregano, salt, and pepper. Form into patties.', 'Grill for 5-6 minutes per side. Serve on whole wheat buns with roasted bell peppers.', 'Cooking time: 12 minutes']</t>
         </is>
@@ -7249,82 +7609,87 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italian Grilled Chicken with Roasted Brussels Sprouts</t>
+          <t>Italian Grilled Chicken With Roasted Brussels Sprouts</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>1564</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '1 tbsp olive oil', '½ tsp salt', '½ tsp black pepper', '2 cups roasted Brussels sprouts']</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "15", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>4</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>10</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N73" t="b">
-        <v>0</v>
-      </c>
       <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="b">
         <v>1</v>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr">
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and pepper.', 'Grill for 6-7 minutes per side. Serve with roasted Brussels sprouts.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -7343,82 +7708,87 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lemon Garlic Shrimp with Roasted Asparagus</t>
+          <t>Lemon Garlic Shrimp With Roasted Asparagus</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '2 cups roasted asparagus']</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve with roasted asparagus.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "8", "fiber": "3", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>4</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>10</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
       <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="b">
         <v>1</v>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve with roasted asparagus.
 3. Cooking time: 5 minutes</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.', 'Serve with roasted asparagus.', 'Cooking time: 5 minutes']</t>
         </is>
@@ -7442,10 +7812,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tsp dried rosemary', '½ tsp salt', '½ tsp black pepper', '2 cups roasted sweet potatoes']</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in rosemary, salt, and black pepper.
@@ -7453,59 +7828,59 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "40", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>4</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>10</v>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N75" t="b">
-        <v>0</v>
-      </c>
       <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="b">
         <v>1</v>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in rosemary, salt, and black pepper.
@@ -7513,8 +7888,8 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr">
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in rosemary, salt, and black pepper.', 'Serve with roasted sweet potatoes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -7533,82 +7908,87 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italian Grilled Chicken with Roasted Eggplant</t>
+          <t>Italian Grilled Chicken With Roasted Eggplant</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '½ tsp salt', '½ tsp black pepper', '2 cups roasted eggplant']</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>4</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>10</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N76" t="b">
-        <v>0</v>
-      </c>
       <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="b">
         <v>1</v>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr">
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and pepper.', 'Grill for 6-7 minutes per side. Serve with roasted eggplant.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -7632,10 +8012,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups steamed spinach']</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add salmon, salt, and pepper. Cook for 5 minutes per side.
@@ -7643,59 +8028,59 @@
 4. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "6", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>4</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>10</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N77" t="b">
-        <v>0</v>
-      </c>
       <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="b">
         <v>1</v>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add salmon, salt, and pepper. Cook for 5 minutes per side.
@@ -7703,8 +8088,8 @@
 4. Cooking time: 12 minutes</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr">
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add salmon, salt, and pepper. Cook for 5 minutes per side.', 'Serve with steamed spinach.', 'Cooking time: 12 minutes']</t>
         </is>
@@ -7723,15 +8108,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italian Grilled Turkey with Pesto &amp; Roasted Peppers</t>
+          <t>Italian Grilled Turkey With Pesto &amp; Roasted Peppers</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>['1 lb. turkey breast, grilled', '2 tbsp olive oil', '1 tbsp pesto sauce', '½ tsp salt', '½ tsp black pepper', '1 cup roasted bell peppers']</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>1. Rub turkey with olive oil, salt, and black pepper.
 2. Grill for 6-7 minutes per side.
@@ -7739,59 +8129,59 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "10", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>4</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>10</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N78" t="b">
-        <v>0</v>
-      </c>
       <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="b">
         <v>1</v>
       </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
         <is>
           <t>1. Rub turkey with olive oil, salt, and black pepper.
 2. Grill for 6-7 minutes per side.
@@ -7799,8 +8189,8 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr">
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
         <is>
           <t>['Rub turkey with olive oil, salt, and black pepper.', 'Grill for 6-7 minutes per side.', 'Top with pesto and serve with roasted bell peppers.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -7824,10 +8214,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 tbsp olive oil', '1 cup cooked lentils', '½ tsp salt', '½ tsp black pepper', '½ tsp dried oregano']</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and oregano.
 2. Grill for 6-7 minutes per side, then slice.
@@ -7835,59 +8230,59 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "42", "fiber": "8", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>4</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>10</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N79" t="b">
-        <v>0</v>
-      </c>
       <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="b">
         <v>1</v>
       </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and oregano.
 2. Grill for 6-7 minutes per side, then slice.
@@ -7895,8 +8290,8 @@
 4. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr">
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and oregano.', 'Grill for 6-7 minutes per side, then slice.', 'Serve over cooked lentils.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -7915,15 +8310,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italian Grilled Swordfish with Roasted Tomatoes</t>
+          <t>Italian Grilled Swordfish With Roasted Tomatoes</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>['4 swordfish fillets', '2 tbsp olive oil', '1 tsp dried Italian herbs', '½ tsp salt', '½ tsp black pepper', '1 cup cherry tomatoes, roasted']</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>1. Rub swordfish with olive oil, Italian herbs, salt, and black pepper.
 2. Grill for 5 minutes per side.
@@ -7931,59 +8331,59 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "8", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>10</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N80" t="b">
-        <v>0</v>
-      </c>
       <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="b">
         <v>1</v>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
         <is>
           <t>1. Rub swordfish with olive oil, Italian herbs, salt, and black pepper.
 2. Grill for 5 minutes per side.
@@ -7991,8 +8391,8 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr">
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
         <is>
           <t>['Rub swordfish with olive oil, Italian herbs, salt, and black pepper.', 'Grill for 5 minutes per side.', 'Serve with roasted tomatoes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -8016,77 +8416,82 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>1572</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '1 cup cooked farro']</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over farro.
 3. Cooking time: 4 minutes</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "42", "fiber": "6", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>4</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>10</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N81" t="b">
-        <v>0</v>
-      </c>
       <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="b">
         <v>1</v>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Serve over farro.
 3. Cooking time: 4 minutes</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr">
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.', 'Serve over farro.', 'Cooking time: 4 minutes']</t>
         </is>
@@ -8110,77 +8515,82 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tsp dried basil', '½ tsp salt', '½ tsp black pepper', '2 zucchinis, sliced and roasted']</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>1. Mix ground turkey with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes. Serve with roasted zucchini.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "54", "carbs": "12", "fiber": "3", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>4</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>10</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N82" t="b">
-        <v>0</v>
-      </c>
       <c r="O82" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" t="b">
         <v>1</v>
       </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
         <is>
           <t>1. Mix ground turkey with basil, salt, and pepper. Form into meatballs.
 2. Heat olive oil in a pan, cook meatballs for 10 minutes. Serve with roasted zucchini.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr">
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
         <is>
           <t>['Mix ground turkey with basil, salt, and pepper. Form into meatballs.', 'Heat olive oil in a pan, cook meatballs for 10 minutes. Serve with roasted zucchini.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -8204,77 +8614,82 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups roasted eggplant']</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, garlic, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "12", "fiber": "5", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>4</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>10</v>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N83" t="b">
-        <v>0</v>
-      </c>
       <c r="O83" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" t="b">
         <v>1</v>
       </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, garlic, salt, and black pepper.
 2. Grill for 6-7 minutes per side. Serve with roasted eggplant.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr">
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, garlic, salt, and black pepper.', 'Grill for 6-7 minutes per side. Serve with roasted eggplant.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -8298,77 +8713,82 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>['1 lb. shrimp, peeled and deveined', '2 tbsp olive oil', 'Juice of 1 lemon', '½ tsp salt', '½ tsp black pepper', '2 zucchinis, sliced and grilled']</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Grill zucchini slices for 3 minutes per side. Serve shrimp with zucchini.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>{"calories": "510", "protein": "54", "carbs": "8", "fiber": "3", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>4</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>10</v>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N84" t="b">
-        <v>0</v>
-      </c>
       <c r="O84" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" t="b">
         <v>1</v>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr">
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.
 2. Grill zucchini slices for 3 minutes per side. Serve shrimp with zucchini.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr">
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook shrimp with lemon juice, salt, and pepper for 4 minutes.', 'Grill zucchini slices for 3 minutes per side. Serve shrimp with zucchini.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -8392,10 +8812,15 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 tbsp balsamic vinegar', '½ tsp salt', '½ tsp black pepper', '2 cups roasted Brussels sprouts']</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in balsamic vinegar, salt, and black pepper.
@@ -8403,59 +8828,59 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "15", "fiber": "5", "fat": "18"}</t>
         </is>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>4</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>10</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N85" t="b">
-        <v>0</v>
-      </c>
       <c r="O85" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" t="b">
         <v>1</v>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in balsamic vinegar, salt, and black pepper.
@@ -8463,8 +8888,8 @@
 4. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr">
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in balsamic vinegar, salt, and black pepper.', 'Serve with roasted Brussels sprouts.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -8488,77 +8913,82 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>['4 tuna steaks', '2 tbsp olive oil', '1 tsp dried oregano', '½ tsp salt', '½ tsp black pepper', '1 cup cherry tomatoes, roasted']</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>1. Rub tuna with olive oil, oregano, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve with roasted cherry tomatoes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "8", "fiber": "3", "fat": "16"}</t>
         </is>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>4</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>10</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N86" t="b">
-        <v>0</v>
-      </c>
       <c r="O86" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" t="b">
         <v>1</v>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr">
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
         <is>
           <t>1. Rub tuna with olive oil, oregano, salt, and black pepper.
 2. Grill for 5 minutes per side. Serve with roasted cherry tomatoes.
 3. Cooking time: 10 minutes</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr">
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
         <is>
           <t>['Rub tuna with olive oil, oregano, salt, and black pepper.', 'Grill for 5 minutes per side. Serve with roasted cherry tomatoes.', 'Cooking time: 10 minutes']</t>
         </is>
@@ -8582,77 +9012,82 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>['1 lb. chicken breast, grilled and sliced', '1 tbsp olive oil', '1 cup cooked chickpeas', '½ tsp salt', '½ tsp black pepper', '1 tsp dried basil']</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and basil.
 2. Grill for 6-7 minutes per side. Serve with chickpeas.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>{"calories": "520", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>4</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>10</v>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N87" t="b">
-        <v>0</v>
-      </c>
       <c r="O87" t="b">
+        <v>0</v>
+      </c>
+      <c r="P87" t="b">
         <v>1</v>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
         <is>
           <t>1. Rub chicken with olive oil, salt, and basil.
 2. Grill for 6-7 minutes per side. Serve with chickpeas.
 3. Cooking time: 14 minutes</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr">
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
         <is>
           <t>['Rub chicken with olive oil, salt, and basil.', 'Grill for 6-7 minutes per side. Serve with chickpeas.', 'Cooking time: 14 minutes']</t>
         </is>
@@ -8676,10 +9111,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>['4 swordfish fillets', '2 tbsp olive oil', '2 cloves garlic, minced', '½ tsp salt', '½ tsp black pepper', '2 cups steamed asparagus']</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add swordfish, salt, and pepper. Cook for 5 minutes per side.
@@ -8687,59 +9127,59 @@
 4. Cooking time: 11 minutes</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>{"calories": "540", "protein": "55", "carbs": "6", "fiber": "3", "fat": "20"}</t>
         </is>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>4</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>10</v>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain', 'seafood']</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N88" t="b">
-        <v>0</v>
-      </c>
       <c r="O88" t="b">
+        <v>0</v>
+      </c>
+      <c r="P88" t="b">
         <v>1</v>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr">
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook garlic for 1 minute.
 2. Add swordfish, salt, and pepper. Cook for 5 minutes per side.
@@ -8747,8 +9187,8 @@
 4. Cooking time: 11 minutes</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr">
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook garlic for 1 minute.', 'Add swordfish, salt, and pepper. Cook for 5 minutes per side.', 'Serve with steamed asparagus.', 'Cooking time: 11 minutes']</t>
         </is>
@@ -8772,77 +9212,82 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>['1 lb. ground turkey', '1 tbsp olive oil', '1 cup white beans, cooked', '½ tsp salt', '½ tsp black pepper', '1 tsp dried basil']</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in white beans, basil, salt, and black pepper. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>{"calories": "530", "protein": "55", "carbs": "30", "fiber": "7", "fat": "14"}</t>
         </is>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>4</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>10</v>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>['muscle-gain', 'lunches-and-dinners', 'salads', 'pasta', 'rice', 'stews', 'seafood', 'ethnic', 'italian']</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>['animal-protein', 'ethnic', 'italian', 'lunches-and-dinners', 'muscle-gain']</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>with_oil</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>muscle_gain</t>
         </is>
       </c>
-      <c r="N89" t="b">
-        <v>0</v>
-      </c>
       <c r="O89" t="b">
+        <v>0</v>
+      </c>
+      <c r="P89" t="b">
         <v>1</v>
       </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr">
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
         <is>
           <t>1. Heat olive oil in a pan, cook turkey until browned.
 2. Stir in white beans, basil, salt, and black pepper. Simmer for 10 minutes.
 3. Cooking time: 15 minutes</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr">
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
         <is>
           <t>['Heat olive oil in a pan, cook turkey until browned.', 'Stir in white beans, basil, salt, and black pepper. Simmer for 10 minutes.', 'Cooking time: 15 minutes']</t>
         </is>
